--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.53847909119092</v>
+        <v>2.525002852318525</v>
       </c>
       <c r="D2" t="n">
-        <v>15.24643877464201</v>
+        <v>2.477546300879327</v>
       </c>
       <c r="E2" t="n">
-        <v>5.273866083613454</v>
+        <v>0.8570032385871862</v>
       </c>
       <c r="F2" t="n">
-        <v>5.082235869340543</v>
+        <v>0.8258633287678383</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.95340370445072</v>
+        <v>3.729928101973242</v>
       </c>
       <c r="D3" t="n">
-        <v>24.68448124044804</v>
+        <v>4.011228201572807</v>
       </c>
       <c r="E3" t="n">
-        <v>5.273866083613454</v>
+        <v>0.8570032385871862</v>
       </c>
       <c r="F3" t="n">
-        <v>5.082235869340543</v>
+        <v>0.8258633287678383</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.5075506650864</v>
+        <v>3.81997698307654</v>
       </c>
       <c r="D4" t="n">
-        <v>23.95409101707458</v>
+        <v>3.89253979027462</v>
       </c>
       <c r="E4" t="n">
-        <v>5.273866083613454</v>
+        <v>0.8570032385871862</v>
       </c>
       <c r="F4" t="n">
-        <v>5.082235869340543</v>
+        <v>0.8258633287678383</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.7705950734714</v>
+        <v>3.700221699439103</v>
       </c>
       <c r="D5" t="n">
-        <v>24.89434190325575</v>
+        <v>4.045330559279059</v>
       </c>
       <c r="E5" t="n">
-        <v>5.273866083613454</v>
+        <v>0.8570032385871862</v>
       </c>
       <c r="F5" t="n">
-        <v>5.082235869340543</v>
+        <v>0.8258633287678383</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.83395763560933</v>
+        <v>2.248018115786516</v>
       </c>
       <c r="D6" t="n">
-        <v>29.36891461679501</v>
+        <v>4.77244862522919</v>
       </c>
       <c r="E6" t="n">
-        <v>5.273866083613454</v>
+        <v>0.8570032385871862</v>
       </c>
       <c r="F6" t="n">
-        <v>5.082235869340543</v>
+        <v>0.8258633287678383</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.55816287524137</v>
+        <v>4.803201467226723</v>
       </c>
       <c r="D7" t="n">
-        <v>31.29307023691347</v>
+        <v>5.085123913498439</v>
       </c>
       <c r="E7" t="n">
-        <v>5.273866083613454</v>
+        <v>0.8570032385871862</v>
       </c>
       <c r="F7" t="n">
-        <v>5.082235869340543</v>
+        <v>0.8258633287678383</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
